--- a/data/Awards.xlsx
+++ b/data/Awards.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -18,26 +18,51 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$C$1:$Z$1</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
   <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Título Original</t>
+  </si>
+  <si>
+    <t>Título</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t>Año</t>
   </si>
   <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Título</t>
-  </si>
-  <si>
-    <t>Título Original</t>
+    <t>Organización Original</t>
+  </si>
+  <si>
+    <t>Organización</t>
+  </si>
+  <si>
+    <t>Professional Activities</t>
   </si>
   <si>
     <t>Premio a la reutilización de datos abiertos</t>
@@ -58,6 +83,9 @@
     <t>Accésit Premios de Investigación Margarita Salas (Tesis)</t>
   </si>
   <si>
+    <t>Margarita Salas Scientific Research Award (Honorable Mention)</t>
+  </si>
+  <si>
     <t>Premio Extraordinario de Doctorado</t>
   </si>
   <si>
@@ -70,6 +98,9 @@
     <t>Technical University of Madrid</t>
   </si>
   <si>
+    <t>Prfoessional Activities</t>
+  </si>
+  <si>
     <t>Paul Baran Young Scholar Award</t>
   </si>
   <si>
@@ -79,6 +110,9 @@
     <t>Marconi Society</t>
   </si>
   <si>
+    <t>Teaching</t>
+  </si>
+  <si>
     <t>Premio al Grupo de Innovación Educativa CyberAula</t>
   </si>
   <si>
@@ -88,6 +122,9 @@
     <t>Accésit Mejor Tesis Cátedra Zarco del Valle</t>
   </si>
   <si>
+    <t>Zarco del Valle Chair Best Thesis (Honorable Mention)</t>
+  </si>
+  <si>
     <t>Tercer premio concurso #HiloTesis</t>
   </si>
   <si>
@@ -145,25 +182,7 @@
     <t>Mathematical Kangaroo</t>
   </si>
   <si>
-    <t>Organización Original</t>
-  </si>
-  <si>
-    <t>Organización</t>
-  </si>
-  <si>
-    <t>Prfoessional Activities</t>
-  </si>
-  <si>
-    <t>Professional Activities</t>
-  </si>
-  <si>
-    <t>Teaching</t>
-  </si>
-  <si>
-    <t>Zarco del Valle Chair Best Thesis (Honorable Mention)</t>
-  </si>
-  <si>
-    <t>Margarita Salas Scientific Research Award (Honorable Mention)</t>
+    <t>Grant</t>
   </si>
   <si>
     <t>Ayudas para estancias de investigación internacional (PDI e investigadores doctores)</t>
@@ -172,66 +191,49 @@
     <t>Grants for international research stays (PDI and PhD researchers)</t>
   </si>
   <si>
+    <t>UPM</t>
+  </si>
+  <si>
     <t>Ayudas Programa Propio UPM-Santander para contratos predoctorales (Mención Internacional)</t>
   </si>
   <si>
     <t>UPM-Santander Program Grants for Pre-doctoral Contracts (International Mention)</t>
   </si>
   <si>
+    <t>UPM-Santander</t>
+  </si>
+  <si>
     <t>Beca de Excelencia de la Comunidad de Madrid</t>
   </si>
   <si>
     <t>Community of Madrid Excellence Scholarship</t>
   </si>
   <si>
+    <t>Comunidad de Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community of Madrid </t>
+  </si>
+  <si>
     <t>Reconocimiento mejores expedientes de Selectividad (USC)</t>
   </si>
   <si>
     <t>Recognition for Top University Entrance Exam Records (USC)</t>
   </si>
   <si>
-    <t xml:space="preserve">Community of Madrid </t>
+    <t>Comunidad de Galicia</t>
   </si>
   <si>
     <t>Community of Galicia</t>
-  </si>
-  <si>
-    <t>Comunidad de Madrid</t>
-  </si>
-  <si>
-    <t>Comunidad de Galicia</t>
-  </si>
-  <si>
-    <t>UPM-Santander</t>
-  </si>
-  <si>
-    <t>UPM</t>
-  </si>
-  <si>
-    <t>Grant</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -313,56 +315,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -669,55 +669,55 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="27.5" style="11" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" style="11" customWidth="1"/>
     <col min="2" max="2" width="100" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.5" style="8" customWidth="1"/>
-    <col min="4" max="4" width="5.83203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="85.42578125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="8" customWidth="1"/>
     <col min="5" max="5" width="36" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="18.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="18.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="51" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.85546875" style="8" bestFit="1" customWidth="1"/>
     <col min="22" max="24" width="24" style="8" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="24" style="8" customWidth="1"/>
-    <col min="26" max="26" width="12.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.83203125" style="11"/>
+    <col min="26" max="26" width="12.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="8" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" s="8" customFormat="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -742,384 +742,731 @@
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:29">
+      <c r="A2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="14">
+        <v>2025</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="16"/>
+      <c r="AC2" s="16"/>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="14">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="14">
+        <v>2025</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="16"/>
+      <c r="AB4" s="16"/>
+      <c r="AC4" s="16"/>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="15"/>
+      <c r="E5" s="14">
+        <v>2024</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="14">
+        <v>2024</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="14">
+        <v>2023</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="14">
+        <v>2022</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.95" customHeight="1">
+      <c r="A9" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="14">
+        <v>2022</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+    </row>
+    <row r="10" spans="1:29" ht="30.95" customHeight="1">
+      <c r="A10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="14">
+        <v>2020</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="14">
+        <v>2018</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="14">
+        <v>2014</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="16"/>
+      <c r="AC12" s="16"/>
+    </row>
+    <row r="13" spans="1:29" ht="15.95" customHeight="1">
+      <c r="A13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="18">
+      <c r="C13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="14">
+        <v>2014</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+    </row>
+    <row r="14" spans="1:29" ht="17.100000000000001">
+      <c r="A14" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="14">
         <v>2025</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="18">
-        <v>2025</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="F14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
+      <c r="AC14" s="16"/>
+    </row>
+    <row r="15" spans="1:29" ht="17.100000000000001">
+      <c r="A15" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="14">
+        <v>2023</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+    </row>
+    <row r="16" spans="1:29" ht="17.100000000000001">
+      <c r="A16" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="14">
+        <v>2020</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
+      <c r="AC16" s="16"/>
+    </row>
+    <row r="17" spans="1:7" ht="17.100000000000001">
+      <c r="A17" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="18">
-        <v>2025</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="18">
-        <v>2024</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="18">
-        <v>2024</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="18">
-        <v>2023</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="18">
-        <v>2022</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="18">
-        <v>2022</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="18">
-        <v>2020</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="18">
-        <v>2018</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="12"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="18">
+      <c r="B17" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="14">
+        <v>2017</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17.100000000000001">
+      <c r="A18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="14">
+        <v>2015</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17.100000000000001">
+      <c r="A19" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="14">
         <v>2014</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="12"/>
-    </row>
-    <row r="13" spans="1:29" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="18">
-        <v>2014</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="12"/>
-    </row>
-    <row r="14" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
+      <c r="F19" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="18">
-        <v>2025</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" s="12"/>
-    </row>
-    <row r="15" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="18">
-        <v>2023</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:29" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="18">
-        <v>2020</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="18">
-        <v>2017</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="18">
-        <v>2015</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="18">
-        <v>2014</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="F21" s="16"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
